--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126505242</v>
+        <v>126506334</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -809,17 +809,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
+          <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503403</v>
+        <v>503389</v>
       </c>
       <c r="R3" t="n">
-        <v>6851284</v>
+        <v>6851035</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -878,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126506334</v>
+        <v>126506062</v>
       </c>
       <c r="B4" t="n">
         <v>98395</v>
@@ -906,26 +915,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503389</v>
+        <v>503286</v>
       </c>
       <c r="R4" t="n">
-        <v>6851035</v>
+        <v>6851109</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,32 +984,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126506062</v>
+        <v>126506164</v>
       </c>
       <c r="B5" t="n">
-        <v>98395</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503286</v>
+        <v>503232</v>
       </c>
       <c r="R5" t="n">
-        <v>6851109</v>
+        <v>6851127</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1081,45 +1081,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126506164</v>
+        <v>126505242</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björntorraken, Björntorraken, Hls</t>
+          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503232</v>
+        <v>503403</v>
       </c>
       <c r="R6" t="n">
-        <v>6851127</v>
+        <v>6851284</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126506334</v>
+        <v>126506062</v>
       </c>
       <c r="B3" t="n">
         <v>98395</v>
@@ -809,26 +809,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503389</v>
+        <v>503286</v>
       </c>
       <c r="R3" t="n">
-        <v>6851035</v>
+        <v>6851109</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126506062</v>
+        <v>126506164</v>
       </c>
       <c r="B4" t="n">
-        <v>98395</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503286</v>
+        <v>503232</v>
       </c>
       <c r="R4" t="n">
-        <v>6851109</v>
+        <v>6851127</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,45 +975,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126506164</v>
+        <v>126506334</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>98395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503232</v>
+        <v>503389</v>
       </c>
       <c r="R5" t="n">
-        <v>6851127</v>
+        <v>6851035</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126506390</v>
+        <v>126506284</v>
       </c>
       <c r="B7" t="n">
-        <v>98395</v>
+        <v>105381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,43 +1189,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granbarkarna, Granbarkarna, Hls</t>
+          <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503493</v>
+        <v>503352</v>
       </c>
       <c r="R7" t="n">
-        <v>6851005</v>
+        <v>6851055</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1284,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126506284</v>
+        <v>126506390</v>
       </c>
       <c r="B8" t="n">
-        <v>105381</v>
+        <v>98395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,34 +1286,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björntorraken, Björntorraken, Hls</t>
+          <t>Granbarkarna, Granbarkarna, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503352</v>
+        <v>503493</v>
       </c>
       <c r="R8" t="n">
-        <v>6851055</v>
+        <v>6851005</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126505473</v>
+        <v>126505147</v>
       </c>
       <c r="B12" t="n">
-        <v>105381</v>
+        <v>98278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,21 +1692,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503462</v>
+        <v>503399</v>
       </c>
       <c r="R12" t="n">
-        <v>6851231</v>
+        <v>6851280</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126505147</v>
+        <v>126505473</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>105381</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503399</v>
+        <v>503462</v>
       </c>
       <c r="R13" t="n">
-        <v>6851280</v>
+        <v>6851231</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126504328</v>
+        <v>126505435</v>
       </c>
       <c r="B14" t="n">
         <v>98278</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503513</v>
+        <v>503440</v>
       </c>
       <c r="R14" t="n">
-        <v>6851134</v>
+        <v>6851238</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126505435</v>
+        <v>126504328</v>
       </c>
       <c r="B15" t="n">
         <v>98278</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503440</v>
+        <v>503513</v>
       </c>
       <c r="R15" t="n">
-        <v>6851238</v>
+        <v>6851134</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126504551</v>
+        <v>126506297</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>98395</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2468,34 +2468,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
+          <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503525</v>
+        <v>503365</v>
       </c>
       <c r="R20" t="n">
-        <v>6851148</v>
+        <v>6851064</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126506297</v>
+        <v>126504551</v>
       </c>
       <c r="B21" t="n">
-        <v>98395</v>
+        <v>98278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2565,34 +2565,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björntorraken, Björntorraken, Hls</t>
+          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503365</v>
+        <v>503525</v>
       </c>
       <c r="R21" t="n">
-        <v>6851064</v>
+        <v>6851148</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126506062</v>
+        <v>126506164</v>
       </c>
       <c r="B3" t="n">
-        <v>98395</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503286</v>
+        <v>503232</v>
       </c>
       <c r="R3" t="n">
-        <v>6851109</v>
+        <v>6851127</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -878,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126506164</v>
+        <v>126505242</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>98382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björntorraken, Björntorraken, Hls</t>
+          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503232</v>
+        <v>503403</v>
       </c>
       <c r="R4" t="n">
-        <v>6851127</v>
+        <v>6851284</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126506334</v>
+        <v>126506062</v>
       </c>
       <c r="B5" t="n">
         <v>98395</v>
@@ -1003,26 +1003,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503389</v>
+        <v>503286</v>
       </c>
       <c r="R5" t="n">
-        <v>6851035</v>
+        <v>6851109</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1081,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126505242</v>
+        <v>126506334</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>98395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,16 +1083,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1109,17 +1100,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
+          <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503403</v>
+        <v>503389</v>
       </c>
       <c r="R6" t="n">
-        <v>6851284</v>
+        <v>6851035</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126505708</v>
+        <v>126505473</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>105381</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503390</v>
+        <v>503462</v>
       </c>
       <c r="R11" t="n">
-        <v>6851200</v>
+        <v>6851231</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1681,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126505147</v>
+        <v>126505708</v>
       </c>
       <c r="B12" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503399</v>
+        <v>503390</v>
       </c>
       <c r="R12" t="n">
-        <v>6851280</v>
+        <v>6851200</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126505473</v>
+        <v>126505147</v>
       </c>
       <c r="B13" t="n">
-        <v>105381</v>
+        <v>98278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503462</v>
+        <v>503399</v>
       </c>
       <c r="R13" t="n">
-        <v>6851231</v>
+        <v>6851280</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126506164</v>
+        <v>126506062</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>98395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503232</v>
+        <v>503286</v>
       </c>
       <c r="R3" t="n">
-        <v>6851127</v>
+        <v>6851109</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -878,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126505242</v>
+        <v>126506164</v>
       </c>
       <c r="B4" t="n">
-        <v>98382</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
+          <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503403</v>
+        <v>503232</v>
       </c>
       <c r="R4" t="n">
-        <v>6851284</v>
+        <v>6851127</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126506062</v>
+        <v>126506334</v>
       </c>
       <c r="B5" t="n">
         <v>98395</v>
@@ -1003,17 +1003,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björntorraken, Björntorraken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503286</v>
+        <v>503389</v>
       </c>
       <c r="R5" t="n">
-        <v>6851109</v>
+        <v>6851035</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126506334</v>
+        <v>126505242</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,16 +1092,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1100,26 +1109,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björntorraken, Björntorraken, Hls</t>
+          <t>Granbarksbäcken, Granbarksbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503389</v>
+        <v>503403</v>
       </c>
       <c r="R6" t="n">
-        <v>6851035</v>
+        <v>6851284</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126505473</v>
+        <v>126505708</v>
       </c>
       <c r="B11" t="n">
-        <v>105381</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503462</v>
+        <v>503390</v>
       </c>
       <c r="R11" t="n">
-        <v>6851231</v>
+        <v>6851200</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1681,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126505708</v>
+        <v>126505147</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>98278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503390</v>
+        <v>503399</v>
       </c>
       <c r="R12" t="n">
-        <v>6851200</v>
+        <v>6851280</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126505147</v>
+        <v>126505473</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>105381</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503399</v>
+        <v>503462</v>
       </c>
       <c r="R13" t="n">
-        <v>6851280</v>
+        <v>6851231</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -2751,7 +2751,7 @@
         <v>126673282</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>126671687</v>
       </c>
       <c r="B24" t="n">
-        <v>103803</v>
+        <v>103878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>126673563</v>
       </c>
       <c r="B25" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126673442</v>
       </c>
       <c r="B26" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>126673624</v>
       </c>
       <c r="B27" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>126673684</v>
       </c>
       <c r="B28" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>126673336</v>
       </c>
       <c r="B29" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -2751,7 +2751,7 @@
         <v>126673282</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>126671687</v>
       </c>
       <c r="B24" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>126673563</v>
       </c>
       <c r="B25" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126673442</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>126673624</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>126673684</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>126673336</v>
       </c>
       <c r="B29" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -2848,7 +2848,7 @@
         <v>126671687</v>
       </c>
       <c r="B24" t="n">
-        <v>103884</v>
+        <v>103885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>126673563</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126673442</v>
       </c>
       <c r="B26" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>126673624</v>
       </c>
       <c r="B27" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>126673684</v>
       </c>
       <c r="B28" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>126673336</v>
       </c>
       <c r="B29" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98711</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>98719</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98719</v>
+        <v>98729</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98729</v>
+        <v>98736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98736</v>
+        <v>98738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98738</v>
+        <v>98764</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98764</v>
+        <v>98765</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98765</v>
+        <v>98766</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98766</v>
+        <v>98770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98770</v>
+        <v>98772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98772</v>
+        <v>98776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98776</v>
+        <v>98784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98784</v>
+        <v>98787</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -3458,7 +3458,7 @@
         <v>126674034</v>
       </c>
       <c r="B30" t="n">
-        <v>98787</v>
+        <v>98816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 32589-2025 artfynd.xlsx
+++ b/artfynd/A 32589-2025 artfynd.xlsx
@@ -2751,7 +2751,7 @@
         <v>126673282</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>126671687</v>
       </c>
       <c r="B24" t="n">
-        <v>103885</v>
+        <v>103878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>126673563</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>126673442</v>
       </c>
       <c r="B26" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>126673624</v>
       </c>
       <c r="B27" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>126673684</v>
       </c>
       <c r="B28" t="n">
-        <v>98477</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>126673336</v>
       </c>
       <c r="B29" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
